--- a/data/trans_bre/IP2002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 8,27</t>
+          <t>-3,54; 9,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 2,11</t>
+          <t>-6,68; 2,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 8,15</t>
+          <t>-2,04; 9,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 8,27</t>
+          <t>-4,55; 7,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 238,83</t>
+          <t>-41,78; 289,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 163,69</t>
+          <t>-100,0; 173,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,7; 776,55</t>
+          <t>-53,03; 902,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 209,97</t>
+          <t>-44,1; 188,85</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 8,02</t>
+          <t>-3,15; 8,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 4,1</t>
+          <t>-4,81; 4,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,3</t>
+          <t>-4,6; 3,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 7,28</t>
+          <t>-3,35; 7,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 542,86</t>
+          <t>-54,11; 495,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,77; 279,14</t>
+          <t>-85,23; 374,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,27; 314,68</t>
+          <t>-86,41; 294,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 539,22</t>
+          <t>-67,96; 479,32</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 7,44</t>
+          <t>-4,63; 7,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 2,62</t>
+          <t>-6,43; 2,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 7,18</t>
+          <t>-6,67; 7,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 12,41</t>
+          <t>-3,87; 12,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,85; 252,14</t>
+          <t>-67,68; 281,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 178,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,37; 246,06</t>
+          <t>-73,69; 226,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,3; 854,73</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,98</t>
+          <t>-4,56; 2,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,78</t>
+          <t>-4,42; 4,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,98</t>
+          <t>-5,1; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,85</t>
+          <t>-3,15; 4,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,26; 69,92</t>
+          <t>-55,58; 70,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,19; 85,21</t>
+          <t>-51,96; 90,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,76; 73,6</t>
+          <t>-59,2; 60,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 164,65</t>
+          <t>-47,49; 163,9</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 2,58</t>
+          <t>-9,03; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 4,63</t>
+          <t>-8,43; 4,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 10,6</t>
+          <t>-0,75; 10,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 7,33</t>
+          <t>-1,91; 7,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 33,95</t>
+          <t>-68,16; 42,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 57,16</t>
+          <t>-54,62; 56,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 632,72</t>
+          <t>-20,39; 607,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 535,02</t>
+          <t>-60,84; 483,9</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,72</t>
+          <t>-7,36; 6,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 0,99</t>
+          <t>-11,94; 1,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 11,52</t>
+          <t>-1,67; 12,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 6,73</t>
+          <t>-8,67; 6,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,71; 180,32</t>
+          <t>-69,71; 192,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,08</t>
+          <t>-100,0; 119,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 1295,98</t>
+          <t>-57,15; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,16</t>
+          <t>-2,56; 2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,99</t>
+          <t>-3,42; 1,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,43</t>
+          <t>-0,86; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,83</t>
+          <t>-0,83; 3,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 39,67</t>
+          <t>-32,28; 34,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 18,83</t>
+          <t>-43,0; 20,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 86,58</t>
+          <t>-15,87; 90,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 101,2</t>
+          <t>-15,53; 102,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 9,26</t>
+          <t>-3,67; 8,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,33</t>
+          <t>-6,7; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 9,25</t>
+          <t>-1,89; 8,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 7,52</t>
+          <t>-3,61; 8,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 289,22</t>
+          <t>-44,79; 285,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 173,8</t>
+          <t>-100,0; 130,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 902,45</t>
+          <t>-54,59; 931,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 188,85</t>
+          <t>-41,75; 241,64</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 8,26</t>
+          <t>-3,45; 7,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 4,53</t>
+          <t>-5,07; 4,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 3,25</t>
+          <t>-4,93; 3,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 7,06</t>
+          <t>-2,99; 7,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 495,98</t>
+          <t>-64,15; 415,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,23; 374,49</t>
+          <t>-88,64; 302,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,41; 294,42</t>
+          <t>-87,86; 308,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 479,32</t>
+          <t>-63,17; 397,1</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 7,62</t>
+          <t>-5,52; 8,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,66</t>
+          <t>-6,27; 2,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 7,24</t>
+          <t>-6,49; 7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 12,41</t>
+          <t>-4,79; 11,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 281,35</t>
+          <t>-71,36; 242,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,54</t>
+          <t>-100,0; 355,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 226,21</t>
+          <t>-76,92; 264,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,3; 854,73</t>
+          <t>-84,03; 672,07</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 2,82</t>
+          <t>-5,01; 2,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,0</t>
+          <t>-4,04; 4,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,84</t>
+          <t>-5,31; 2,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,75</t>
+          <t>-3,15; 4,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 70,74</t>
+          <t>-57,96; 69,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 90,49</t>
+          <t>-48,26; 87,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 60,88</t>
+          <t>-58,2; 58,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 163,9</t>
+          <t>-48,83; 146,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 3,0</t>
+          <t>-9,41; 2,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 4,43</t>
+          <t>-7,46; 5,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 10,12</t>
+          <t>0,18; 10,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 7,33</t>
+          <t>-2,25; 7,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,16; 42,18</t>
+          <t>-68,35; 41,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 56,31</t>
+          <t>-50,58; 63,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 607,37</t>
+          <t>-12,54; 623,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 483,9</t>
+          <t>-66,12; 580,63</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 6,18</t>
+          <t>-8,05; 5,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 1,31</t>
+          <t>-12,4; 0,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 12,96</t>
+          <t>-2,36; 11,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 6,31</t>
+          <t>-8,7; 7,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,71; 192,73</t>
+          <t>-73,22; 176,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,62</t>
+          <t>-100,0; 66,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,15; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,03</t>
+          <t>-2,62; 1,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,14</t>
+          <t>-3,41; 0,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,48</t>
+          <t>-0,45; 3,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,49</t>
+          <t>-1,11; 3,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 34,14</t>
+          <t>-33,24; 34,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 20,66</t>
+          <t>-43,93; 16,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 90,44</t>
+          <t>-9,26; 94,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 102,35</t>
+          <t>-20,03; 87,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,98</t>
+          <t>-3,99; 8,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 2,01</t>
+          <t>-6,44; 2,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 8,88</t>
+          <t>-2,33; 8,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 8,61</t>
+          <t>-2,99; 8,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 285,14</t>
+          <t>-45,54; 238,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 130,09</t>
+          <t>-100,0; 163,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 931,89</t>
+          <t>-66,7; 776,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 241,64</t>
+          <t>-40,71; 232,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 7,65</t>
+          <t>-3,19; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,15</t>
+          <t>-4,7; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 3,22</t>
+          <t>-4,88; 3,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 7,24</t>
+          <t>-2,92; 7,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 415,89</t>
+          <t>-56,44; 542,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,64; 302,54</t>
+          <t>-85,77; 279,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,86; 308,09</t>
+          <t>-86,27; 314,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 397,1</t>
+          <t>-64,01; 653,52</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 8,0</t>
+          <t>-5,22; 7,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,66</t>
+          <t>-6,21; 2,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 7,74</t>
+          <t>-7,27; 7,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 11,87</t>
+          <t>-4,21; 12,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 242,88</t>
+          <t>-73,85; 252,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 355,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,92; 264,07</t>
+          <t>-73,37; 246,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-84,03; 672,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 2,69</t>
+          <t>-4,52; 2,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,03</t>
+          <t>-4,12; 3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,71</t>
+          <t>-4,94; 2,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,57</t>
+          <t>-1,49; 6,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,96; 69,86</t>
+          <t>-54,26; 69,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 87,94</t>
+          <t>-52,19; 85,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 58,82</t>
+          <t>-56,76; 73,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 146,7</t>
+          <t>-27,18; 231,86</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>86,78%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 2,67</t>
+          <t>-9,89; 2,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 5,06</t>
+          <t>-8,03; 4,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 10,83</t>
+          <t>-0,18; 10,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,41</t>
+          <t>-2,09; 7,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 41,71</t>
+          <t>-71,05; 33,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 63,57</t>
+          <t>-52,68; 57,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 623,82</t>
+          <t>-9,02; 632,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,12; 580,63</t>
+          <t>-64,82; 510,81</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,93</t>
+          <t>-3,91</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-35,63%</t>
+          <t>-75,2%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 5,75</t>
+          <t>-7,45; 5,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 0,74</t>
+          <t>-12,88; 0,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 11,59</t>
+          <t>-2,79; 11,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 7,1</t>
+          <t>-10,96; 0,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,22; 176,65</t>
+          <t>-73,71; 180,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,77</t>
+          <t>-100,0; 123,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,73; 1295,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,98</t>
+          <t>-2,66; 2,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,9</t>
+          <t>-3,33; 0,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,74</t>
+          <t>-0,77; 3,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,31</t>
+          <t>-0,45; 3,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 34,77</t>
+          <t>-32,69; 39,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,93; 16,62</t>
+          <t>-43,37; 18,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 94,74</t>
+          <t>-13,61; 86,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 87,43</t>
+          <t>-9,25; 108,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-46,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39,81%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.50420211750117</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.129249737563403</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.61388106343981</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.549879054871737</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3939881053670534</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4646823848164257</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.8677933789654649</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.3981223551513969</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 8,27</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,44; 2,11</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,33; 8,15</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,99; 8,98</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-45,54; 238,83</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 163,69</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-66,7; 776,55</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-40,71; 232,4</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.992796827951341</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.442091323691017</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.326499311788254</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.99035392090372</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4554477567753077</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6670397460560643</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4070716359071352</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.265297339905397</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.106081614336398</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.154419338106718</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.982931657110401</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.388260437099484</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.636944298171835</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>7.765480396749456</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.323980188162988</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>50,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-12,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-19,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,19; 8,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,7; 4,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; 3,3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,92; 7,46</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-56,44; 542,86</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-85,77; 279,14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-86,27; 314,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-64,01; 653,52</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.061216520111017</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.4645500618859467</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6712695719735376</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2.04662655678897</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.5050103848927049</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1253063131260402</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.197603743460799</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.613540097426598</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-37,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>57,28%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.192529258839734</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.700936173939916</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.879195184984946</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.915832965229151</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5644349462752848</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8576897998942894</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.8626613872319546</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6400998946526906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,22; 7,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,21; 2,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,27; 7,18</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 12,57</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-73,85; 252,14</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-73,37; 246,06</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.018892589275067</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.102997331763437</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.295021257720782</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.463418219753645</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>5.428570272203497</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.791375285980444</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3.146778453813469</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>6.535188320474253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-14,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-16,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47,82%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.8639212029612854</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.505789949794894</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.346319685706932</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.767127473663288</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1516847374808575</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3751026910989576</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.05216520969968935</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.5728487598139107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; 2,98</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 3,78</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 2,98</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,49; 6,52</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-54,26; 69,92</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-52,19; 85,21</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-56,76; 73,6</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-27,18; 231,86</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.224027306452895</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.213550372198986</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.269245777398598</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.20587710013921</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.7384632783941021</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-0.7336643865929405</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.437754194365424</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.620383687567899</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.182911394471176</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.57106248707758</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.521448587447424</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>2.460626139156469</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-3,59</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-33,14%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-11,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>134,8%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>86,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-9,89; 2,58</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-8,03; 4,63</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 10,6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 7,27</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-71,05; 33,95</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-52,68; 57,16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-9,02; 632,72</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-64,82; 510,81</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.905251833632216</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.08461518861510309</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.109480875891298</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.235605776940051</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1420932526225546</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.0130781843968086</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1628122078215028</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.4781863552560782</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-5,06</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4,13</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-3,91</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-8,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-65,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>118,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-75,2%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.520392905711969</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.121997834089902</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.941789161086125</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.485907529558792</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5425642336368856</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5218845419696582</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5675704426222015</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2718452386818498</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-7,45; 5,72</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-12,88; 0,99</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 11,52</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-10,96; 0,46</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-73,71; 180,32</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 123,08</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-67,73; 1295,98</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.983818161551726</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.784586905005913</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.977720195290932</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.516931500698978</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6992278300804979</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8520640839853804</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7359790142057347</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.318641587744242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1011,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,77%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-18,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36,67%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-3.586454794410318</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.313968553260396</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.104792617796011</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.548022855184564</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.3314368613792595</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1139164707144849</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1.347997835296282</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.8678259582903358</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 2,16</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 0,99</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 3,43</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 3,85</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-32,69; 39,67</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-43,37; 18,83</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-13,61; 86,58</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-9,25; 108,37</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-9.887785421206424</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.027101521461054</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.1758940794029714</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.087562535134183</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7104968305799831</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.5268103012958331</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.09018497215857221</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6481852014849686</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.580733453812966</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.628430104168404</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>10.60217737995404</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.271788508476392</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3394960666185902</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5716477120236676</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>6.327221783755518</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>5.108087792170291</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-0.6222349297943242</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-5.055866461208826</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>4.133058107690818</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-3.905819818618239</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.08936463346486485</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.6553570222751812</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1.185604658528995</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.7519530458644399</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-7.452374679315723</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-12.88326870484246</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-2.790455551967921</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-10.96326104671661</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.737084998557917</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.6772615628978257</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>5.722520827081355</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.9915564455947202</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>11.5247403356837</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.4584234296971275</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.803202850634339</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.230782718754351</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>12.95976881200478</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.258772277531738</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-1.20892602860922</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.378513908141971</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.649911218104079</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.03767870427744736</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.1809288032846686</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.2864840792152077</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.3666679903885994</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.657929074835979</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.334761498969776</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.7654200937844388</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.4471210972840949</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3268845353830333</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4337367465690473</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1361189971546951</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.0925083292050083</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.16034982781515</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.9919287520607549</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.431256508076905</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.84871634486608</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.3966765147649771</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.1883114015910077</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.8658103771048831</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1.083690821785464</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1305,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
